--- a/file/temp/class/DAPC_ProyectoCAD_2025_02_Grupo5.xlsx
+++ b/file/temp/class/DAPC_ProyectoCAD_2025_02_Grupo5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9AC2E6-51DF-4C9B-946E-6B1C46624644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3CC916D-F5B6-4693-98B8-7A50955CD4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="733" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="7" r:id="rId1"/>
@@ -332,7 +332,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="46">
+  <futureMetadata name="XLRICHVALUE" count="12">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -417,251 +417,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="13"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="14"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="15"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="16"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="17"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="18"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="19"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="20"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="21"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="22"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="23"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="24"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="25"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="26"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="27"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="28"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="29"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="30"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="31"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="32"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="33"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="34"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="35"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="36"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="37"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="38"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="39"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="40"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="41"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="42"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="43"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="44"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="45"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="46">
+  <valueMetadata count="12">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -698,114 +460,12 @@
     <bk>
       <rc t="2" v="11"/>
     </bk>
-    <bk>
-      <rc t="2" v="12"/>
-    </bk>
-    <bk>
-      <rc t="2" v="13"/>
-    </bk>
-    <bk>
-      <rc t="2" v="14"/>
-    </bk>
-    <bk>
-      <rc t="2" v="15"/>
-    </bk>
-    <bk>
-      <rc t="2" v="16"/>
-    </bk>
-    <bk>
-      <rc t="2" v="17"/>
-    </bk>
-    <bk>
-      <rc t="2" v="18"/>
-    </bk>
-    <bk>
-      <rc t="2" v="19"/>
-    </bk>
-    <bk>
-      <rc t="2" v="20"/>
-    </bk>
-    <bk>
-      <rc t="2" v="21"/>
-    </bk>
-    <bk>
-      <rc t="2" v="22"/>
-    </bk>
-    <bk>
-      <rc t="2" v="23"/>
-    </bk>
-    <bk>
-      <rc t="2" v="24"/>
-    </bk>
-    <bk>
-      <rc t="2" v="25"/>
-    </bk>
-    <bk>
-      <rc t="2" v="26"/>
-    </bk>
-    <bk>
-      <rc t="2" v="27"/>
-    </bk>
-    <bk>
-      <rc t="2" v="28"/>
-    </bk>
-    <bk>
-      <rc t="2" v="29"/>
-    </bk>
-    <bk>
-      <rc t="2" v="30"/>
-    </bk>
-    <bk>
-      <rc t="2" v="31"/>
-    </bk>
-    <bk>
-      <rc t="2" v="32"/>
-    </bk>
-    <bk>
-      <rc t="2" v="33"/>
-    </bk>
-    <bk>
-      <rc t="2" v="34"/>
-    </bk>
-    <bk>
-      <rc t="2" v="35"/>
-    </bk>
-    <bk>
-      <rc t="2" v="36"/>
-    </bk>
-    <bk>
-      <rc t="2" v="37"/>
-    </bk>
-    <bk>
-      <rc t="2" v="38"/>
-    </bk>
-    <bk>
-      <rc t="2" v="39"/>
-    </bk>
-    <bk>
-      <rc t="2" v="40"/>
-    </bk>
-    <bk>
-      <rc t="2" v="41"/>
-    </bk>
-    <bk>
-      <rc t="2" v="42"/>
-    </bk>
-    <bk>
-      <rc t="2" v="43"/>
-    </bk>
-    <bk>
-      <rc t="2" v="44"/>
-    </bk>
-    <bk>
-      <rc t="2" v="45"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="569">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1521,9 +1181,6 @@
     <t>Indique la referencia y cantidad de elementos a almacenar en la bodega. Para la distribución en estantes, los transformadores grandes se almacenan en la parte inferior, los medianos en los estantes intermedios y los livianos en la parte superior.</t>
   </si>
   <si>
-    <t>Calcular</t>
-  </si>
-  <si>
     <t>Corresponde al número de pisos que tendrá la estantería incluído el piso a nivel de placa.</t>
   </si>
   <si>
@@ -1549,15 +1206,6 @@
   </si>
   <si>
     <t>Valor longitudinal por número de niveles.</t>
-  </si>
-  <si>
-    <t>Transformador 1 - Ref: #####</t>
-  </si>
-  <si>
-    <t>Transformador 2 - Ref: #####</t>
-  </si>
-  <si>
-    <t>Transformador 3 - Ref: #####</t>
   </si>
   <si>
     <t>Plano de planta general</t>
@@ -2701,6 +2349,39 @@
   </si>
   <si>
     <t>Solidos no integrados.</t>
+  </si>
+  <si>
+    <t>Tercio 2</t>
+  </si>
+  <si>
+    <t>Solo 1 formato con dimensiones de A5?. Faltaron los A0 horizontal y vertical y A4 horizontal.</t>
+  </si>
+  <si>
+    <t>Puertas. Ventanas dibujadas como líneas.</t>
+  </si>
+  <si>
+    <t>No dibujada.</t>
+  </si>
+  <si>
+    <t>Sin líneas conectoras.</t>
+  </si>
+  <si>
+    <t>Falto dibujar la acometida y las líneas conectoras de tomacorrientes.</t>
+  </si>
+  <si>
+    <t>Transformador 1 - Ref: 75 KVA 720003003752</t>
+  </si>
+  <si>
+    <t>Transformador 2 - Ref: 45 KBA Ele45tri</t>
+  </si>
+  <si>
+    <t>Transformador 3 - Ref: 10 KVA 720003001101</t>
+  </si>
+  <si>
+    <t>Sin dimensionamiento.</t>
+  </si>
+  <si>
+    <t>No indicado.</t>
   </si>
 </sst>
 </file>
@@ -3392,7 +3073,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3896,6 +3577,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -4016,6 +3700,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4214,11 +3902,15 @@
     <address r:id="rId19"/>
     <blip r:id="rId20"/>
   </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId21"/>
+    <blip r:id="rId22"/>
+  </webImageSrd>
 </webImagesSrd>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="46">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
   <rv s="0">
     <v>0</v>
     <v>1</v>
@@ -4279,218 +3971,12 @@
     <v>0</v>
     <v>0</v>
   </rv>
+  <rv s="1">
+    <v>12</v>
+    <v>1</v>
+  </rv>
   <rv s="0">
     <v>10</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>11</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>12</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>13</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>14</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>15</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>16</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>17</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>18</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>19</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>20</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>21</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>22</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>23</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>24</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>25</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>26</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>27</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>28</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>29</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>30</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>31</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>32</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>33</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>34</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>0</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>1</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>2</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>3</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>4</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>5</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>6</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>7</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>8</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>9</v>
-    <v>1</v>
-    <v>0</v>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <v>45</v>
     <v>1</v>
     <v>0</v>
     <v>0</v>
@@ -4506,11 +3992,9 @@
     <k n="ComputedImage" t="b"/>
     <k n="ImageSizing" t="i"/>
   </s>
-  <s t="_webimage">
-    <k n="WebImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="ComputedImage" t="b"/>
-    <k n="ImageSizing" t="i"/>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
   </s>
 </rvStructures>
 </file>
@@ -4779,121 +4263,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
   <dimension ref="B1:I39"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="2"/>
-    <col min="8" max="8" width="15.44140625" style="2" customWidth="1"/>
+    <col min="1" max="2" width="2.53125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.53125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.1328125" style="2"/>
+    <col min="8" max="8" width="15.46484375" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="10" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.45">
       <c r="E1" s="12" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
-        <v>467</v>
-      </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B2" s="175" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
       <c r="E2" s="109"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="181" t="s">
-        <v>371</v>
-      </c>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B3" s="182" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
       <c r="E3" s="108"/>
     </row>
-    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
+    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
       <c r="E4" s="107"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
       <c r="E5" s="107"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="167"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
       <c r="E6" s="107"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="186" t="s">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B7" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="187"/>
-      <c r="D7" s="187"/>
-      <c r="E7" s="188"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="185">
-        <v>5</v>
-      </c>
-      <c r="C8" s="169"/>
-      <c r="D8" s="169"/>
-      <c r="E8" s="170"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="182" t="s">
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="189"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B8" s="186">
+        <v>5</v>
+      </c>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="171"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="183"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="184"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="185" t="s">
-        <v>495</v>
-      </c>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="170"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="171"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="173"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="182" t="s">
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="185"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B10" s="186" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="171"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B11" s="172"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="174"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B12" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="183"/>
-      <c r="D12" s="183"/>
-      <c r="E12" s="184"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="168" t="s">
-        <v>496</v>
-      </c>
-      <c r="C13" s="169"/>
-      <c r="D13" s="169"/>
-      <c r="E13" s="170"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="172"/>
-      <c r="E14" s="173"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C12" s="184"/>
+      <c r="D12" s="184"/>
+      <c r="E12" s="185"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B13" s="169" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
+      <c r="E13" s="171"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B14" s="172"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="174"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B15" s="64" t="s">
         <v>11</v>
       </c>
@@ -4902,24 +4386,24 @@
       <c r="E15" s="64"/>
       <c r="G15" s="109"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B16" s="65"/>
       <c r="C16" s="65"/>
       <c r="D16" s="65"/>
       <c r="E16" s="65"/>
       <c r="G16" s="142" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H16" s="143"/>
       <c r="I16" s="85"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="174" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="174"/>
-      <c r="D17" s="174"/>
-      <c r="E17" s="174"/>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B17" s="175" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="175"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
       <c r="G17" s="144">
         <v>0.3</v>
       </c>
@@ -4928,7 +4412,7 @@
       </c>
       <c r="I17" s="146"/>
     </row>
-    <row r="18" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B18" s="43" t="s">
         <v>4</v>
       </c>
@@ -4942,21 +4426,21 @@
         <v>3</v>
       </c>
       <c r="G18" s="147" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H18" s="148" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="I18" s="149" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B19" s="67">
         <v>1</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D19" s="13">
         <v>1000110139</v>
@@ -4967,22 +4451,22 @@
       </c>
       <c r="G19" s="150">
         <f>$E$39</f>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H19" s="151">
         <v>4</v>
       </c>
       <c r="I19" s="152">
         <f>G19*$G$17+H19*$H$17</f>
-        <v>4.2766129032258062</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.1311666666666662</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B20" s="67">
         <v>2</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D20" s="13">
         <v>1000109969</v>
@@ -4993,22 +4477,22 @@
       </c>
       <c r="G20" s="150">
         <f t="shared" ref="G20:G28" si="1">$E$39</f>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H20" s="151">
         <v>5</v>
       </c>
       <c r="I20" s="152">
         <f t="shared" ref="I20:I28" si="2">G20*$G$17+H20*$H$17</f>
-        <v>4.9766129032258064</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.8311666666666664</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B21" s="67">
         <v>3</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D21" s="13">
         <v>1000109704</v>
@@ -5019,22 +4503,22 @@
       </c>
       <c r="G21" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H21" s="151">
         <v>4</v>
       </c>
       <c r="I21" s="152">
         <f t="shared" si="2"/>
-        <v>4.2766129032258062</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.1311666666666662</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B22" s="67">
         <v>4</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D22" s="13">
         <v>1000108372</v>
@@ -5045,22 +4529,22 @@
       </c>
       <c r="G22" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H22" s="151">
         <v>4.5</v>
       </c>
       <c r="I22" s="152">
         <f t="shared" si="2"/>
-        <v>4.6266129032258068</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.4811666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B23" s="67">
         <v>5</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D23" s="13">
         <v>1000109930</v>
@@ -5071,22 +4555,22 @@
       </c>
       <c r="G23" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H23" s="151">
         <v>4.7</v>
       </c>
       <c r="I23" s="152">
         <f t="shared" si="2"/>
-        <v>4.7666129032258064</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.6211666666666664</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B24" s="67">
         <v>6</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D24" s="13">
         <v>1000107941</v>
@@ -5097,17 +4581,17 @@
       </c>
       <c r="G24" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H24" s="151">
         <v>4.8</v>
       </c>
       <c r="I24" s="152">
         <f t="shared" si="2"/>
-        <v>4.8366129032258058</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.6911666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B25" s="67">
         <v>7</v>
       </c>
@@ -5119,15 +4603,15 @@
       </c>
       <c r="G25" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H25" s="151"/>
       <c r="I25" s="152">
         <f t="shared" si="2"/>
-        <v>1.4766129032258064</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1.3311666666666666</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B26" s="67">
         <v>8</v>
       </c>
@@ -5139,15 +4623,15 @@
       </c>
       <c r="G26" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H26" s="151"/>
       <c r="I26" s="152">
         <f t="shared" si="2"/>
-        <v>1.4766129032258064</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1.3311666666666666</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B27" s="67">
         <v>9</v>
       </c>
@@ -5159,15 +4643,15 @@
       </c>
       <c r="G27" s="150">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H27" s="151"/>
       <c r="I27" s="152">
         <f t="shared" si="2"/>
-        <v>1.4766129032258064</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1.3311666666666666</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B28" s="68">
         <v>10</v>
       </c>
@@ -5179,128 +4663,128 @@
       </c>
       <c r="G28" s="153">
         <f t="shared" si="1"/>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
       <c r="H28" s="154"/>
       <c r="I28" s="155">
         <f t="shared" si="2"/>
-        <v>1.4766129032258064</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1.3311666666666666</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
       <c r="D29" s="69" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E29" s="50">
         <f>SUM(E19:E28)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="174" t="s">
-        <v>241</v>
-      </c>
-      <c r="C31" s="174"/>
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B31" s="175" t="s">
+        <v>237</v>
+      </c>
+      <c r="C31" s="175"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B32" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="177" t="s">
+      <c r="C32" s="178" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="178"/>
+      <c r="D32" s="179"/>
       <c r="E32" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" s="44">
         <v>1</v>
       </c>
-      <c r="C33" s="179" t="s">
-        <v>242</v>
-      </c>
-      <c r="D33" s="180"/>
+      <c r="C33" s="180" t="s">
+        <v>238</v>
+      </c>
+      <c r="D33" s="181"/>
       <c r="E33" s="112">
         <f>IF('1.Tecnica'!I19&gt;0,'1.Tecnica'!I19,"")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="44">
         <v>2</v>
       </c>
-      <c r="C34" s="175" t="s">
-        <v>278</v>
-      </c>
-      <c r="D34" s="176"/>
+      <c r="C34" s="176" t="s">
+        <v>274</v>
+      </c>
+      <c r="D34" s="177"/>
       <c r="E34" s="112">
         <f>IF('2.ArquitectonicaEstructural'!I95&gt;0,'2.ArquitectonicaEstructural'!I95,"")</f>
-        <v>4.7661290322580649</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+        <v>4.8066666666666666</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" s="44">
         <v>3</v>
       </c>
-      <c r="C35" s="175" t="s">
-        <v>243</v>
-      </c>
-      <c r="D35" s="176"/>
+      <c r="C35" s="176" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="177"/>
       <c r="E35" s="112">
         <f>IF('3.Electrica'!I28&gt;0,'3.Electrica'!I28,"")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" s="44">
         <v>4</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D36" s="52"/>
-      <c r="E36" s="112" t="str">
+      <c r="E36" s="112">
         <f>IF('4.Bodegaje'!I23&gt;0,'4.Bodegaje'!I23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" s="44">
         <v>4</v>
       </c>
-      <c r="C37" s="175" t="s">
+      <c r="C37" s="176" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="177"/>
+      <c r="E37" s="112">
+        <f>IF('5.Planos'!I17&gt;0,'5.Planos'!I17,"")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="45">
+        <v>5</v>
+      </c>
+      <c r="C38" s="165" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" s="166"/>
+      <c r="E38" s="141">
+        <f>IF('6.Archivos'!H18&gt;0,'6.Archivos'!H18,"")</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D39" s="139" t="s">
         <v>244</v>
-      </c>
-      <c r="D37" s="176"/>
-      <c r="E37" s="112" t="str">
-        <f>IF('5.Planos'!I17&gt;0,'5.Planos'!I17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="45">
-        <v>5</v>
-      </c>
-      <c r="C38" s="164" t="s">
-        <v>245</v>
-      </c>
-      <c r="D38" s="165"/>
-      <c r="E38" s="141" t="str">
-        <f>IF('6.Archivos'!H18&gt;0,'6.Archivos'!H18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D39" s="139" t="s">
-        <v>248</v>
       </c>
       <c r="E39" s="140">
         <f>AVERAGE(E33:E38)</f>
-        <v>4.922043010752688</v>
+        <v>4.4372222222222222</v>
       </c>
     </row>
   </sheetData>
@@ -5338,63 +4822,63 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="3.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.77734375" style="46" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="31" customWidth="1"/>
-    <col min="9" max="9" width="2.77734375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.796875" style="46" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.796875" style="46" customWidth="1"/>
+    <col min="8" max="8" width="12.796875" style="31" customWidth="1"/>
+    <col min="9" max="9" width="2.796875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="174" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B2" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="181" t="s">
-        <v>301</v>
-      </c>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="181"/>
-    </row>
-    <row r="4" spans="2:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
-        <v>302</v>
-      </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B3" s="182" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
+    </row>
+    <row r="4" spans="2:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
@@ -5404,10 +4888,10 @@
       <c r="D6" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="195" t="s">
+      <c r="E6" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="196"/>
+      <c r="F6" s="197"/>
       <c r="G6" s="35" t="s">
         <v>16</v>
       </c>
@@ -5415,18 +4899,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B7" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F7" s="53" t="str">
         <f t="shared" ref="F7:F17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
@@ -5437,18 +4921,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B8" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F8" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5457,18 +4941,18 @@
       <c r="G8" s="48"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="102" x14ac:dyDescent="0.45">
       <c r="B9" s="16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F9" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5477,18 +4961,18 @@
       <c r="G9" s="48"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B10" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F10" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5497,18 +4981,18 @@
       <c r="G10" s="48"/>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B11" s="16" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F11" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5517,18 +5001,18 @@
       <c r="G11" s="48"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B12" s="16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F12" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5537,18 +5021,18 @@
       <c r="G12" s="48"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F13" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5557,35 +5041,37 @@
       <c r="G13" s="48"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="76.5" x14ac:dyDescent="0.45">
       <c r="B14" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G14" s="48"/>
+      <c r="H14" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="E14" s="55" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" s="53" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>274</v>
-      </c>
       <c r="C15" s="19" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E15" s="48"/>
       <c r="F15" s="53" t="str">
@@ -5595,18 +5081,18 @@
       <c r="G15" s="48"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B16" s="27" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D16" s="98" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F16" s="53" t="str">
         <f t="shared" si="0"/>
@@ -5615,7 +5101,7 @@
       <c r="G16" s="99"/>
       <c r="H16" s="100"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="4"/>
@@ -5627,13 +5113,13 @@
       <c r="G17" s="32"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
       <c r="G18" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H18" s="31">
         <f>AVERAGE(H7:H17)</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -5651,27 +5137,27 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD4CBC5-BEDD-4E97-A57A-4EDFE72E7B14}">
   <dimension ref="B1:B4"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="100.77734375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100.796875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B1" s="12"/>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B4" s="11" t="s">
         <v>15</v>
       </c>
@@ -5686,129 +5172,129 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A6E610-5846-4CB7-B250-30076D117F0D}">
-  <dimension ref="B2:F17"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:H17"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="50.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="50.5546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="24.21875" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="2" customWidth="1"/>
+    <col min="3" max="4" width="50.53125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="50.53125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="2.53125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.86328125" style="46" customWidth="1"/>
+    <col min="9" max="9" width="24.19921875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="109" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
       <c r="F2" s="109"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="181" t="s">
-        <v>504</v>
-      </c>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
-        <v>505</v>
-      </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-    </row>
-    <row r="5" spans="2:6" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B3" s="182" t="s">
+        <v>500</v>
+      </c>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
+        <v>501</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+    </row>
+    <row r="5" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="116" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E5" s="113" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="67.2" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="66" x14ac:dyDescent="0.45">
       <c r="B6" s="16" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C6" s="117" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D6" s="118" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E6" s="131">
         <v>5</v>
       </c>
       <c r="F6" s="119" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="117.6" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="99" x14ac:dyDescent="0.45">
       <c r="B7" s="16" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D7" s="118" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E7" s="131">
         <v>7</v>
       </c>
       <c r="F7" s="120"/>
     </row>
-    <row r="8" spans="2:6" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B8" s="16" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C8" s="117" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E8" s="131">
         <v>5</v>
       </c>
       <c r="F8" s="119" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D9" s="121"/>
       <c r="E9" s="131"/>
       <c r="F9" s="122"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B10" s="16" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C10" s="117" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D10" s="121"/>
       <c r="E10" s="131">
@@ -5816,62 +5302,75 @@
       </c>
       <c r="F10" s="122"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B11" s="16" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C11" s="117" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D11" s="121"/>
       <c r="E11" s="131"/>
       <c r="F11" s="122"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B12" s="16" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C12" s="117" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D12" s="121"/>
       <c r="E12" s="131"/>
       <c r="F12" s="122"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="H12" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>440</v>
-      </c>
-      <c r="D13" s="121"/>
+        <v>436</v>
+      </c>
+      <c r="D13" s="118" t="s">
+        <v>559</v>
+      </c>
       <c r="E13" s="131"/>
       <c r="F13" s="122"/>
-    </row>
-    <row r="14" spans="2:6" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="H13" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B14" s="16" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C14" s="117" t="s">
-        <v>514</v>
-      </c>
-      <c r="D14" s="121"/>
+        <v>510</v>
+      </c>
+      <c r="D14" s="118" t="s">
+        <v>563</v>
+      </c>
       <c r="E14" s="131"/>
       <c r="F14" s="122"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="H14" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B15" s="24"/>
       <c r="C15" s="123"/>
       <c r="D15" s="124"/>
       <c r="E15" s="132"/>
       <c r="F15" s="125"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="126"/>
       <c r="C16" s="127"/>
       <c r="D16" s="128" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E16" s="129">
         <f>SUM(E6:E15)</f>
@@ -5879,9 +5378,9 @@
       </c>
       <c r="F16" s="130"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B17" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -5895,64 +5394,66 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B949BBA-AF80-4E1F-814D-4E818DFDC8C8}">
-  <dimension ref="A2:H77"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:J77"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="72" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="70.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" style="31" customWidth="1"/>
-    <col min="5" max="5" width="7.5546875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="3.5546875" style="31" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="72" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" style="31" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.53125" style="72" customWidth="1"/>
+    <col min="2" max="2" width="13.53125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="70.53125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.53125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="7.53125" style="31" customWidth="1"/>
+    <col min="6" max="6" width="3.53125" style="31" customWidth="1"/>
+    <col min="7" max="7" width="10.53125" style="72" customWidth="1"/>
+    <col min="8" max="8" width="12.53125" style="31" customWidth="1"/>
+    <col min="9" max="9" width="2.59765625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.1328125" style="46"/>
+    <col min="11" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
-    </row>
-    <row r="6" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+    </row>
+    <row r="6" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="21" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="E6" s="195" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="196"/>
+      <c r="F6" s="197"/>
       <c r="G6" s="104" t="s">
         <v>16</v>
       </c>
@@ -5960,42 +5461,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="197" t="s">
-        <v>445</v>
-      </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="199"/>
-    </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="192"/>
-      <c r="C8" s="193"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="193"/>
-      <c r="F8" s="193"/>
-      <c r="G8" s="193"/>
-      <c r="H8" s="194"/>
-    </row>
-    <row r="9" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="198" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="200"/>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="193"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
+      <c r="E8" s="194"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="195"/>
+    </row>
+    <row r="9" spans="1:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A9" s="72">
         <v>1</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D9" s="15" t="e" vm="1">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E9,"/graph/",B9,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F9" s="70" t="str">
         <f t="shared" ref="F9:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E9,"/Readme.md#ejercicio-",B9),"Ver")</f>
@@ -6006,200 +5507,200 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="51" x14ac:dyDescent="0.45">
       <c r="A10" s="72">
         <v>2</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D10" s="15" t="e" vm="2">
         <f t="shared" ref="D10:D16" si="1">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E10,"/graph/",B10,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E10" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F10" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H10" s="39">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.45">
       <c r="A11" s="72">
         <v>3</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F11" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G11" s="55" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H11" s="39">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.45">
       <c r="A12" s="72">
         <v>4</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D12" s="15" t="e" vm="3">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F12" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G12" s="110" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H12" s="111">
         <v>4.5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A13" s="72">
         <v>5</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D13" s="15" t="e" vm="4">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="E13" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F13" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G13" s="110" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H13" s="111">
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="89.25" x14ac:dyDescent="0.45">
       <c r="A14" s="72">
         <v>6</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D14" s="15" t="e" vm="5">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F14" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G14" s="110" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H14" s="111">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A15" s="72">
         <v>7</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D15" s="15" t="e" vm="6">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="E15" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F15" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G15" s="110" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H15" s="111">
         <v>4.5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A16" s="72">
         <v>8</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D16" s="15" t="e" vm="7">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="E16" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F16" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="G16" s="110" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H16" s="111">
         <v>2.5</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="26"/>
@@ -6208,9 +5709,9 @@
       <c r="G17" s="56"/>
       <c r="H17" s="41"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B18" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6219,19 +5720,19 @@
       <c r="G18" s="57"/>
       <c r="H18" s="38"/>
     </row>
-    <row r="19" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A19" s="72">
         <v>9</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="55" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F19" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E19,"/Readme.md#ejercicio-",B19),"Ver")</f>
@@ -6242,7 +5743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B20" s="24"/>
       <c r="C20" s="25"/>
       <c r="D20" s="26"/>
@@ -6251,42 +5752,42 @@
       <c r="G20" s="56"/>
       <c r="H20" s="41"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="189" t="s">
-        <v>451</v>
-      </c>
-      <c r="C21" s="190"/>
-      <c r="D21" s="190"/>
-      <c r="E21" s="190"/>
-      <c r="F21" s="190"/>
-      <c r="G21" s="190"/>
-      <c r="H21" s="191"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="192"/>
-      <c r="C22" s="193"/>
-      <c r="D22" s="193"/>
-      <c r="E22" s="193"/>
-      <c r="F22" s="193"/>
-      <c r="G22" s="193"/>
-      <c r="H22" s="194"/>
-    </row>
-    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B21" s="190" t="s">
+        <v>447</v>
+      </c>
+      <c r="C21" s="191"/>
+      <c r="D21" s="191"/>
+      <c r="E21" s="191"/>
+      <c r="F21" s="191"/>
+      <c r="G21" s="191"/>
+      <c r="H21" s="192"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B22" s="193"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="194"/>
+      <c r="G22" s="194"/>
+      <c r="H22" s="195"/>
+    </row>
+    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="72">
         <v>10</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D23" s="15" t="e" vm="8">
         <f t="shared" ref="D23:D31" si="2">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E23,"/graph/",B23,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E23" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F23" s="70" t="str">
         <f t="shared" ref="F23:F31" si="3">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E23,"/Readme.md#ejercicio-",B23),"Ver")</f>
@@ -6297,22 +5798,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="72">
         <v>11</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D24" s="15" t="e" vm="9">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E24" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F24" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6323,22 +5824,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="72">
         <v>12</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D25" s="15" t="e" vm="10">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E25" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F25" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6349,50 +5850,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="72">
         <v>13</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D26" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E26" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F26" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="G26" s="156" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="H26" s="157">
         <v>4.75</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="72">
         <v>14</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="D27" s="15" t="e" vm="12">
+        <v>450</v>
+      </c>
+      <c r="D27" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E27" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F27" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6403,22 +5904,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="72">
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="D28" s="15" t="e" vm="13">
+        <v>451</v>
+      </c>
+      <c r="D28" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E28" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F28" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6429,22 +5930,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="72">
         <v>16</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="D29" s="15" t="e" vm="14">
+        <v>452</v>
+      </c>
+      <c r="D29" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E29" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F29" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6455,22 +5956,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="72">
         <v>17</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="D30" s="15" t="e" vm="15">
+        <v>452</v>
+      </c>
+      <c r="D30" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E30" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F30" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6481,35 +5982,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="72">
         <v>18</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>457</v>
-      </c>
-      <c r="D31" s="15" t="e" vm="16">
+        <v>453</v>
+      </c>
+      <c r="D31" s="15" t="e" vm="11">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="E31" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F31" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="G31" s="156" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H31" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="26"/>
@@ -6518,9 +6019,9 @@
       <c r="G32" s="56"/>
       <c r="H32" s="41"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B33" s="5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="18"/>
@@ -6529,22 +6030,22 @@
       <c r="G33" s="57"/>
       <c r="H33" s="38"/>
     </row>
-    <row r="34" spans="1:8" ht="57" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A34" s="72">
         <v>19</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>459</v>
-      </c>
-      <c r="D34" s="15" t="e" vm="17">
+        <v>455</v>
+      </c>
+      <c r="D34" s="15" t="e" vm="11">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E34,"/graph/",B34,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E34" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F34" s="70" t="str">
         <f t="shared" ref="F34:F41" si="4">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E34,"/Readme.md#ejercicio-",B34),"Ver")</f>
@@ -6555,22 +6056,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="79.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A35" s="72">
         <v>20</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="D35" s="15" t="e" vm="18">
+        <v>456</v>
+      </c>
+      <c r="D35" s="15" t="e" vm="11">
         <f t="shared" ref="D35:D41" si="5">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E35,"/graph/",B35,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E35" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F35" s="70" t="str">
         <f t="shared" si="4"/>
@@ -6581,103 +6082,103 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="159.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="165.75" x14ac:dyDescent="0.45">
       <c r="A36" s="72">
         <v>21</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="D36" s="15" t="e" vm="19">
+        <v>457</v>
+      </c>
+      <c r="D36" s="15" t="e" vm="11">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="E36" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F36" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Ver</v>
       </c>
       <c r="G36" s="156" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H36" s="157">
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="72">
         <v>22</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="D37" s="15" t="e" vm="20">
+        <v>383</v>
+      </c>
+      <c r="D37" s="15" t="e" vm="11">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E37,"/graph/",B37,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E37" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F37" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Ver</v>
       </c>
       <c r="G37" s="156" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H37" s="157">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="72">
         <v>23</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F38" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Ver</v>
       </c>
       <c r="G38" s="156" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H38" s="157">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="72">
         <v>24</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>463</v>
-      </c>
-      <c r="D39" s="15" t="e" vm="21">
+        <v>459</v>
+      </c>
+      <c r="D39" s="15" t="e" vm="11">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="E39" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F39" s="70" t="str">
         <f t="shared" si="4"/>
@@ -6688,50 +6189,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="102.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="114.75" x14ac:dyDescent="0.45">
       <c r="A40" s="72">
         <v>25</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="D40" s="15" t="e" vm="22">
+        <v>460</v>
+      </c>
+      <c r="D40" s="15" t="e" vm="11">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="E40" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F40" s="70" t="str">
         <f t="shared" si="4"/>
         <v>Ver</v>
       </c>
       <c r="G40" s="156" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H40" s="157">
         <v>3.5</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="72">
         <v>26</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>465</v>
-      </c>
-      <c r="D41" s="15" t="e" vm="23">
+        <v>461</v>
+      </c>
+      <c r="D41" s="15" t="e" vm="11">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="E41" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F41" s="70" t="str">
         <f t="shared" si="4"/>
@@ -6742,7 +6243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B42" s="27"/>
       <c r="C42" s="28"/>
       <c r="D42" s="29"/>
@@ -6751,42 +6252,42 @@
       <c r="G42" s="58"/>
       <c r="H42" s="40"/>
     </row>
-    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="189" t="s">
-        <v>466</v>
-      </c>
-      <c r="C43" s="190"/>
-      <c r="D43" s="190"/>
-      <c r="E43" s="190"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="190"/>
-      <c r="H43" s="191"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="192"/>
-      <c r="C44" s="193"/>
-      <c r="D44" s="193"/>
-      <c r="E44" s="193"/>
-      <c r="F44" s="193"/>
-      <c r="G44" s="193"/>
-      <c r="H44" s="194"/>
-    </row>
-    <row r="45" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="190" t="s">
+        <v>462</v>
+      </c>
+      <c r="C43" s="191"/>
+      <c r="D43" s="191"/>
+      <c r="E43" s="191"/>
+      <c r="F43" s="191"/>
+      <c r="G43" s="191"/>
+      <c r="H43" s="192"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B44" s="193"/>
+      <c r="C44" s="194"/>
+      <c r="D44" s="194"/>
+      <c r="E44" s="194"/>
+      <c r="F44" s="194"/>
+      <c r="G44" s="194"/>
+      <c r="H44" s="195"/>
+    </row>
+    <row r="45" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="72">
         <v>27</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="D45" s="15" t="e" vm="24">
-        <f t="shared" ref="D45:D64" si="6">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E45,"/graph/",B45,".jpg?raw=true"))</f>
+        <v>388</v>
+      </c>
+      <c r="D45" s="15" t="e" vm="11">
+        <f t="shared" ref="D45:D56" si="6">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E45,"/graph/",B45,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E45" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F45" s="70" t="str">
         <f t="shared" ref="F45:F65" si="7">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E45,"/Readme.md#ejercicio-",B45),"Ver")</f>
@@ -6797,22 +6298,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="72">
         <v>28</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="D46" s="15" t="e" vm="25">
+        <v>390</v>
+      </c>
+      <c r="D46" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E46" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F46" s="70" t="str">
         <f t="shared" si="7"/>
@@ -6823,22 +6324,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="72">
         <v>29</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="D47" s="15" t="e" vm="26">
+        <v>392</v>
+      </c>
+      <c r="D47" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E47" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F47" s="70" t="str">
         <f t="shared" si="7"/>
@@ -6849,50 +6350,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A48" s="72">
         <v>30</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="D48" s="15" t="e" vm="27">
+        <v>394</v>
+      </c>
+      <c r="D48" s="15" t="e" vm="11">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E48,"/graph/",B48,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E48" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F48" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G48" s="156" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H48" s="157">
         <v>4.75</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="72">
         <v>31</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="D49" s="15" t="e" vm="28">
+        <v>396</v>
+      </c>
+      <c r="D49" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E49" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F49" s="70" t="str">
         <f t="shared" si="7"/>
@@ -6903,22 +6404,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="72">
         <v>32</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="D50" s="15" t="e" vm="29">
+        <v>398</v>
+      </c>
+      <c r="D50" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E50" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F50" s="70" t="str">
         <f t="shared" si="7"/>
@@ -6929,50 +6430,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="72">
         <v>33</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="D51" s="15" t="e" vm="30">
+        <v>400</v>
+      </c>
+      <c r="D51" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E51" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F51" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G51" s="156" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H51" s="157">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="72">
         <v>34</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>406</v>
-      </c>
-      <c r="D52" s="15" t="e" vm="31">
+        <v>402</v>
+      </c>
+      <c r="D52" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E52" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F52" s="70" t="str">
         <f t="shared" si="7"/>
@@ -6983,50 +6484,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="72">
         <v>35</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="D53" s="15" t="e" vm="32">
+        <v>404</v>
+      </c>
+      <c r="D53" s="15" t="e" vm="11">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E53,"/graph/",B53,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E53" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F53" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G53" s="156" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H53" s="157">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="72">
         <v>36</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>410</v>
-      </c>
-      <c r="D54" s="15" t="e" vm="33">
+        <v>406</v>
+      </c>
+      <c r="D54" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E54" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F54" s="70" t="str">
         <f t="shared" si="7"/>
@@ -7037,190 +6538,190 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="72">
         <v>37</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="D55" s="15" t="e" vm="34">
+        <v>408</v>
+      </c>
+      <c r="D55" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E55" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F55" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G55" s="156" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H55" s="157">
         <v>4.5</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="72">
         <v>38</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="D56" s="15" t="e" vm="35">
+        <v>410</v>
+      </c>
+      <c r="D56" s="15" t="e" vm="11">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="E56" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F56" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G56" s="156" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H56" s="157">
         <v>4.25</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="51" x14ac:dyDescent="0.45">
       <c r="A57" s="72">
         <v>39</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="D57" s="15" t="e" vm="36">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E57,"/graph/",B57,".jpg?raw=true"))</f>
+        <v>412</v>
+      </c>
+      <c r="D57" s="15" t="e" vm="1">
+        <f t="shared" ref="D57:D64" si="8">_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E57,"/graph/",B57,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E57" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F57" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G57" s="156" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H57" s="157">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="A58" s="72">
         <v>40</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>418</v>
-      </c>
-      <c r="D58" s="15" t="e" vm="37">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E58,"/graph/",B58,".jpg?raw=true"))</f>
+        <v>414</v>
+      </c>
+      <c r="D58" s="15" t="e" vm="2">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E58" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F58" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G58" s="156" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H58" s="157">
         <v>4.75</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="72">
         <v>41</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="D59" s="15" t="e" vm="38">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E59,"/graph/",B59,".jpg?raw=true"))</f>
+        <v>416</v>
+      </c>
+      <c r="D59" s="15" t="e" vm="3">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E59" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F59" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G59" s="156" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H59" s="157">
         <v>4.25</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="72">
         <v>42</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="D60" s="15" t="e" vm="39">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E60,"/graph/",B60,".jpg?raw=true"))</f>
+        <v>418</v>
+      </c>
+      <c r="D60" s="15" t="e" vm="4">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E60" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F60" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G60" s="156" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H60" s="157">
         <v>4.75</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="72">
         <v>43</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="D61" s="15" t="e" vm="40">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E61,"/graph/",B61,".jpg?raw=true"))</f>
+        <v>390</v>
+      </c>
+      <c r="D61" s="15" t="e" vm="5">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E61" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F61" s="70" t="str">
         <f t="shared" si="7"/>
@@ -7231,22 +6732,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="72">
         <v>44</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="D62" s="15" t="e" vm="41">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E62,"/graph/",B62,".jpg?raw=true"))</f>
+        <v>421</v>
+      </c>
+      <c r="D62" s="15" t="e" vm="6">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E62" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F62" s="70" t="str">
         <f t="shared" si="7"/>
@@ -7257,50 +6758,50 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="72">
         <v>45</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="D63" s="15" t="e" vm="42">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E63,"/graph/",B63,".jpg?raw=true"))</f>
+        <v>423</v>
+      </c>
+      <c r="D63" s="15" t="e" vm="7">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E63" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F63" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G63" s="156" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="H63" s="157">
         <v>4.25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="72">
         <v>46</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="D64" s="15" t="e" vm="43">
-        <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E64,"/graph/",B64,".jpg?raw=true"))</f>
+        <v>425</v>
+      </c>
+      <c r="D64" s="15" t="e" vm="8">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="E64" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F64" s="70" t="str">
         <f t="shared" si="7"/>
@@ -7311,32 +6812,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="72">
         <v>47</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F65" s="70" t="str">
         <f t="shared" si="7"/>
         <v>Ver</v>
       </c>
       <c r="G65" s="156" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H65" s="157">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B66" s="27"/>
       <c r="C66" s="28"/>
       <c r="D66" s="29"/>
@@ -7345,9 +6846,9 @@
       <c r="G66" s="58"/>
       <c r="H66" s="163"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B67" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C67" s="17"/>
       <c r="D67" s="18"/>
@@ -7356,22 +6857,22 @@
       <c r="G67" s="57"/>
       <c r="H67" s="38"/>
     </row>
-    <row r="68" spans="1:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A68" s="72">
         <v>48</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="D68" s="15" t="e" vm="44">
+        <v>430</v>
+      </c>
+      <c r="D68" s="15" t="e" vm="9">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E68,"/graph/",B68,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E68" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F68" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E68,"/Readme.md#ejercicio-",B68),"Ver")</f>
@@ -7382,22 +6883,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="72">
         <v>49</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>436</v>
-      </c>
-      <c r="D69" s="15" t="e" vm="45">
+        <v>432</v>
+      </c>
+      <c r="D69" s="15" t="e" vm="10">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E69,"/graph/",B69,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E69" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F69" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E69,"/Readme.md#ejercicio-",B69),"Ver")</f>
@@ -7408,7 +6909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B70" s="27"/>
       <c r="C70" s="28"/>
       <c r="D70" s="29"/>
@@ -7417,9 +6918,9 @@
       <c r="G70" s="58"/>
       <c r="H70" s="40"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B71" s="5" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C71" s="17"/>
       <c r="D71" s="18"/>
@@ -7428,31 +6929,36 @@
       <c r="G71" s="57"/>
       <c r="H71" s="38"/>
     </row>
-    <row r="72" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="72">
         <v>50</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>439</v>
-      </c>
-      <c r="D72" s="15" t="e" vm="46">
+        <v>435</v>
+      </c>
+      <c r="D72" s="15" t="e" vm="12">
         <f>_xlfn.IMAGE(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E72,"/graph/",B72,".jpg?raw=true"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E72" s="55" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F72" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E72,"/Readme.md#ejercicio-",B72),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="G72" s="58"/>
-      <c r="H72" s="40"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H72" s="40">
+        <v>5</v>
+      </c>
+      <c r="J72" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B73" s="27"/>
       <c r="C73" s="28"/>
       <c r="D73" s="29"/>
@@ -7461,9 +6967,9 @@
       <c r="G73" s="58"/>
       <c r="H73" s="40"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B74" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C74" s="17"/>
       <c r="D74" s="18"/>
@@ -7472,28 +6978,35 @@
       <c r="G74" s="57"/>
       <c r="H74" s="38"/>
     </row>
-    <row r="75" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" ht="76.5" x14ac:dyDescent="0.45">
       <c r="A75" s="72">
         <v>51</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D75" s="29"/>
       <c r="E75" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F75" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E75,"/Readme.md#ejercicio-",B75),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="G75" s="58"/>
-      <c r="H75" s="40"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G75" s="156" t="s">
+        <v>559</v>
+      </c>
+      <c r="H75" s="157">
+        <v>1.5</v>
+      </c>
+      <c r="J75" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B76" s="24"/>
       <c r="C76" s="25"/>
       <c r="D76" s="26"/>
@@ -7502,13 +7015,13 @@
       <c r="G76" s="56"/>
       <c r="H76" s="41"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G77" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H77" s="31">
         <f>AVERAGE(H7:H76)</f>
-        <v>4.3928571428571432</v>
+        <v>4.3480392156862742</v>
       </c>
     </row>
   </sheetData>
@@ -7526,49 +7039,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
-  <dimension ref="B1:I19"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:K19"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="46" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="31" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="46" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="2.796875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="46"/>
+    <col min="12" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.45">
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -7581,10 +7095,10 @@
       <c r="E6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="195" t="s">
+      <c r="F6" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="196"/>
+      <c r="G6" s="197"/>
       <c r="H6" s="22" t="s">
         <v>16</v>
       </c>
@@ -7592,12 +7106,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="76.5" x14ac:dyDescent="0.45">
       <c r="B7" s="16" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D7" s="59">
         <v>1</v>
@@ -7606,57 +7120,57 @@
         <v>7</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G7" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H7" s="133" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="I7" s="61">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B8" s="16" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D8" s="59">
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G8" s="70" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="136" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="I8" s="61"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D9" s="59" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="55" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G9" s="70" t="str">
         <f t="shared" si="0"/>
@@ -7667,12 +7181,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B10" s="16" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D10" s="59">
         <v>1</v>
@@ -7681,117 +7195,129 @@
         <v>7</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G10" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="133" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I10" s="61">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="33" x14ac:dyDescent="0.45">
       <c r="B11" s="16" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D11" s="59" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G11" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="133" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I11" s="61">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="63.75" x14ac:dyDescent="0.45">
       <c r="B12" s="16" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="55" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G12" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="133" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="I12" s="61">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D13" s="59" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="55" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G13" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="133"/>
-      <c r="I13" s="61"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="I13" s="61">
+        <v>5</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="33" x14ac:dyDescent="0.45">
       <c r="B14" s="16" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G14" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H14" s="133"/>
-      <c r="I14" s="61"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="H14" s="137" t="s">
+        <v>559</v>
+      </c>
+      <c r="I14" s="203">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B15" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D15" s="59">
         <v>1</v>
@@ -7800,21 +7326,25 @@
         <v>7</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G15" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="133"/>
-      <c r="I15" s="61"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="133" t="s">
+        <v>560</v>
+      </c>
+      <c r="I15" s="61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="52.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="16" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D16" s="59">
         <v>1</v>
@@ -7823,21 +7353,23 @@
         <v>7</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G16" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H16" s="133"/>
-      <c r="I16" s="61"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="35.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="27" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D17" s="59">
         <v>1</v>
@@ -7846,16 +7378,18 @@
         <v>7</v>
       </c>
       <c r="F17" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G17" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H17" s="134"/>
-      <c r="I17" s="62"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B18" s="24"/>
       <c r="C18" s="25"/>
       <c r="D18" s="60"/>
@@ -7868,13 +7402,13 @@
       <c r="H18" s="135"/>
       <c r="I18" s="63"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
       <c r="H19" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I19" s="31">
         <f>AVERAGE(I7:I18)</f>
-        <v>5</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -7897,53 +7431,53 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
   <dimension ref="B2:I105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="72" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="31" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="46" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="31" customWidth="1"/>
-    <col min="10" max="10" width="2.5546875" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="72" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="31" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="46" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="2.53125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B3" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="166" t="s">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B4" s="167" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -7956,10 +7490,10 @@
       <c r="E6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="201"/>
+      <c r="G6" s="202"/>
       <c r="H6" s="22" t="s">
         <v>16</v>
       </c>
@@ -7967,9 +7501,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -7979,7 +7513,7 @@
       <c r="H7" s="47"/>
       <c r="I7" s="38"/>
     </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B8" s="16" t="s">
         <v>142</v>
       </c>
@@ -7993,22 +7527,22 @@
         <v>43</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G8" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="158" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I8" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B9" s="16" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>144</v>
@@ -8020,20 +7554,20 @@
         <v>43</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G9" s="70" t="str">
         <f t="shared" ref="G9:G77" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H9" s="158" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I9" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B10" s="16" t="s">
         <v>147</v>
       </c>
@@ -8048,20 +7582,20 @@
         <v>43</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G10" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="158" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I10" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" s="16" t="s">
         <v>148</v>
       </c>
@@ -8076,20 +7610,20 @@
         <v>43</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G11" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="158" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I11" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B12" s="16" t="s">
         <v>29</v>
       </c>
@@ -8103,20 +7637,20 @@
         <v>43</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G12" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="158" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I12" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B13" s="16" t="s">
         <v>50</v>
       </c>
@@ -8130,20 +7664,20 @@
         <v>43</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G13" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="158" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I13" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B14" s="16" t="s">
         <v>30</v>
       </c>
@@ -8157,20 +7691,20 @@
         <v>43</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G14" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="158" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I14" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B15" s="16" t="s">
         <v>42</v>
       </c>
@@ -8185,20 +7719,20 @@
         <v>43</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G15" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H15" s="158" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I15" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B16" s="16" t="s">
         <v>41</v>
       </c>
@@ -8213,20 +7747,20 @@
         <v>43</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G16" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H16" s="158" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I16" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B17" s="16" t="s">
         <v>40</v>
       </c>
@@ -8241,20 +7775,20 @@
         <v>44</v>
       </c>
       <c r="F17" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G17" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H17" s="158" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="I17" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B18" s="27" t="s">
         <v>87</v>
       </c>
@@ -8269,16 +7803,18 @@
         <v>44</v>
       </c>
       <c r="F18" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G18" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H18" s="28"/>
-      <c r="I18" s="40"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B19" s="27" t="s">
         <v>85</v>
       </c>
@@ -8293,16 +7829,18 @@
         <v>44</v>
       </c>
       <c r="F19" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G19" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H19" s="28"/>
-      <c r="I19" s="40"/>
-    </row>
-    <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="I19" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B20" s="27" t="s">
         <v>56</v>
       </c>
@@ -8317,16 +7855,18 @@
         <v>57</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G20" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H20" s="28"/>
-      <c r="I20" s="40"/>
-    </row>
-    <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="I20" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B21" s="27" t="s">
         <v>86</v>
       </c>
@@ -8341,16 +7881,18 @@
         <v>57</v>
       </c>
       <c r="F21" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G21" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H21" s="28"/>
-      <c r="I21" s="40"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
@@ -8363,9 +7905,9 @@
       <c r="H22" s="25"/>
       <c r="I22" s="41"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B23" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="18"/>
@@ -8375,7 +7917,7 @@
       <c r="H23" s="47"/>
       <c r="I23" s="38"/>
     </row>
-    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B24" s="16" t="s">
         <v>61</v>
       </c>
@@ -8389,7 +7931,7 @@
         <v>43</v>
       </c>
       <c r="F24" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G24" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8400,7 +7942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="63.75" x14ac:dyDescent="0.45">
       <c r="B25" s="16" t="s">
         <v>62</v>
       </c>
@@ -8414,7 +7956,7 @@
         <v>58</v>
       </c>
       <c r="F25" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G25" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8425,7 +7967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B26" s="16" t="s">
         <v>63</v>
       </c>
@@ -8440,7 +7982,7 @@
         <v>59</v>
       </c>
       <c r="F26" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G26" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8451,12 +7993,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B27" s="27" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D27" s="73">
         <v>0.6</v>
@@ -8465,7 +8007,7 @@
         <v>43</v>
       </c>
       <c r="F27" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G27" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8476,7 +8018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B28" s="16" t="s">
         <v>64</v>
       </c>
@@ -8490,20 +8032,20 @@
         <v>43</v>
       </c>
       <c r="F28" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G28" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H28" s="138" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I28" s="111">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B29" s="16" t="s">
         <v>123</v>
       </c>
@@ -8517,7 +8059,7 @@
         <v>57</v>
       </c>
       <c r="F29" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G29" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8528,7 +8070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B30" s="27" t="s">
         <v>66</v>
       </c>
@@ -8543,7 +8085,7 @@
         <v>44</v>
       </c>
       <c r="F30" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G30" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8554,9 +8096,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B31" s="16" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>126</v>
@@ -8569,7 +8111,7 @@
         <v>44</v>
       </c>
       <c r="F31" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G31" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8580,9 +8122,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B32" s="16" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>127</v>
@@ -8595,7 +8137,7 @@
         <v>44</v>
       </c>
       <c r="F32" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G32" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8606,9 +8148,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B33" s="16" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>110</v>
@@ -8620,7 +8162,7 @@
         <v>43</v>
       </c>
       <c r="F33" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G33" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8631,9 +8173,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B34" s="16" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>128</v>
@@ -8646,7 +8188,7 @@
         <v>102</v>
       </c>
       <c r="F34" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G34" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8657,12 +8199,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B35" s="16" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D35" s="15">
         <f>(INT(D10/D33))</f>
@@ -8676,12 +8218,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B36" s="16" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D36" s="15">
         <f>D34/D35</f>
@@ -8695,12 +8237,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B37" s="16" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D37" s="15">
         <f>D10/(D35+1)</f>
@@ -8710,7 +8252,7 @@
         <v>43</v>
       </c>
       <c r="F37" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G37" s="70" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F37,"/Readme.md"),"Ver")</f>
@@ -8721,12 +8263,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B38" s="16" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D38" s="15">
         <f>D11/(D36+1)</f>
@@ -8736,7 +8278,7 @@
         <v>43</v>
       </c>
       <c r="F38" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G38" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8747,9 +8289,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B39" s="16" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>52</v>
@@ -8761,7 +8303,7 @@
         <v>53</v>
       </c>
       <c r="F39" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G39" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8772,12 +8314,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B40" s="16" t="s">
         <v>67</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D40" s="15">
         <f>D39*D39/(1000*1000)</f>
@@ -8787,7 +8329,7 @@
         <v>44</v>
       </c>
       <c r="F40" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G40" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8798,7 +8340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B41" s="16" t="s">
         <v>68</v>
       </c>
@@ -8813,7 +8355,7 @@
         <v>44</v>
       </c>
       <c r="F41" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G41" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8824,7 +8366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B42" s="24"/>
       <c r="C42" s="25"/>
       <c r="D42" s="26"/>
@@ -8837,9 +8379,9 @@
       <c r="H42" s="25"/>
       <c r="I42" s="41"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B43" s="74" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="18"/>
@@ -8849,9 +8391,9 @@
       <c r="H43" s="47"/>
       <c r="I43" s="38"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B44" s="16" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C44" s="19" t="s">
         <v>73</v>
@@ -8863,7 +8405,7 @@
         <v>43</v>
       </c>
       <c r="F44" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G44" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8874,7 +8416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B45" s="16" t="s">
         <v>70</v>
       </c>
@@ -8888,7 +8430,7 @@
         <v>43</v>
       </c>
       <c r="F45" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G45" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8899,12 +8441,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B46" s="16" t="s">
         <v>71</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D46" s="15">
         <f>D11+(INT(D11/D45)*D10)</f>
@@ -8914,7 +8456,7 @@
         <v>43</v>
       </c>
       <c r="F46" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G46" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B47" s="16" t="s">
         <v>72</v>
       </c>
@@ -8940,7 +8482,7 @@
         <v>44</v>
       </c>
       <c r="F47" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G47" s="70" t="str">
         <f t="shared" si="0"/>
@@ -8951,7 +8493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="26"/>
@@ -8964,9 +8506,9 @@
       <c r="H48" s="25"/>
       <c r="I48" s="41"/>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B49" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="18"/>
@@ -8976,12 +8518,12 @@
       <c r="H49" s="47"/>
       <c r="I49" s="38"/>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B50" s="16" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D50" s="20">
         <v>0.15</v>
@@ -8990,7 +8532,7 @@
         <v>43</v>
       </c>
       <c r="F50" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G50" s="70" t="str">
         <f t="shared" ref="G50" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F50,"/Readme.md"),"Ver")</f>
@@ -9001,12 +8543,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B51" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D51" s="20">
         <v>60</v>
@@ -9015,20 +8557,20 @@
         <v>44</v>
       </c>
       <c r="F51" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G51" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H51" s="158" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="I51" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B52" s="16" t="s">
         <v>32</v>
       </c>
@@ -9042,20 +8584,20 @@
         <v>44</v>
       </c>
       <c r="F52" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G52" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H52" s="138" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="I52" s="159">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B53" s="16" t="s">
         <v>76</v>
       </c>
@@ -9069,20 +8611,20 @@
         <v>43</v>
       </c>
       <c r="F53" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G53" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H53" s="138" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="I53" s="111">
         <v>3.5</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B54" s="16" t="s">
         <v>77</v>
       </c>
@@ -9097,7 +8639,7 @@
         <v>44</v>
       </c>
       <c r="F54" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G54" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9108,7 +8650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B55" s="16" t="s">
         <v>47</v>
       </c>
@@ -9122,7 +8664,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G55" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9133,7 +8675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B56" s="16" t="s">
         <v>80</v>
       </c>
@@ -9147,20 +8689,20 @@
         <v>45</v>
       </c>
       <c r="F56" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G56" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H56" s="138" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I56" s="111">
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B57" s="16" t="s">
         <v>78</v>
       </c>
@@ -9175,20 +8717,20 @@
         <v>39</v>
       </c>
       <c r="F57" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G57" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H57" s="138" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I57" s="111">
         <v>3.5</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B58" s="16" t="s">
         <v>81</v>
       </c>
@@ -9202,20 +8744,20 @@
         <v>43</v>
       </c>
       <c r="F58" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G58" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H58" s="138" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I58" s="111">
         <v>4.5</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B59" s="16" t="s">
         <v>83</v>
       </c>
@@ -9230,7 +8772,7 @@
         <v>44</v>
       </c>
       <c r="F59" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G59" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9241,7 +8783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="76.5" x14ac:dyDescent="0.45">
       <c r="B60" s="16" t="s">
         <v>112</v>
       </c>
@@ -9255,16 +8797,18 @@
         <v>43</v>
       </c>
       <c r="F60" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G60" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H60" s="19"/>
-      <c r="I60" s="39"/>
-    </row>
-    <row r="61" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="I60" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="76.5" x14ac:dyDescent="0.45">
       <c r="B61" s="16" t="s">
         <v>113</v>
       </c>
@@ -9278,16 +8822,18 @@
         <v>43</v>
       </c>
       <c r="F61" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G61" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H61" s="19"/>
-      <c r="I61" s="39"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I61" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B62" s="16" t="s">
         <v>115</v>
       </c>
@@ -9301,16 +8847,18 @@
         <v>43</v>
       </c>
       <c r="F62" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G62" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H62" s="19"/>
-      <c r="I62" s="39"/>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I62" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B63" s="16" t="s">
         <v>166</v>
       </c>
@@ -9324,16 +8872,18 @@
         <v>43</v>
       </c>
       <c r="F63" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G63" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H63" s="19"/>
-      <c r="I63" s="39"/>
-    </row>
-    <row r="64" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="I63" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B64" s="16" t="s">
         <v>116</v>
       </c>
@@ -9347,16 +8897,18 @@
         <v>43</v>
       </c>
       <c r="F64" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G64" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H64" s="19"/>
-      <c r="I64" s="39"/>
-    </row>
-    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="I64" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B65" s="16" t="s">
         <v>165</v>
       </c>
@@ -9370,16 +8922,18 @@
         <v>43</v>
       </c>
       <c r="F65" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G65" s="70" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H65" s="19"/>
-      <c r="I65" s="39"/>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I65" s="159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B66" s="24"/>
       <c r="C66" s="25"/>
       <c r="D66" s="26"/>
@@ -9392,9 +8946,9 @@
       <c r="H66" s="25"/>
       <c r="I66" s="41"/>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B67" s="75" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C67" s="76"/>
       <c r="D67" s="77"/>
@@ -9404,7 +8958,7 @@
       <c r="H67" s="79"/>
       <c r="I67" s="80"/>
     </row>
-    <row r="68" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B68" s="16" t="s">
         <v>149</v>
       </c>
@@ -9418,7 +8972,7 @@
         <v>45</v>
       </c>
       <c r="F68" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G68" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9429,9 +8983,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B69" s="16" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>150</v>
@@ -9444,7 +8998,7 @@
         <v>44</v>
       </c>
       <c r="F69" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G69" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9455,7 +9009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B70" s="16" t="s">
         <v>89</v>
       </c>
@@ -9469,7 +9023,7 @@
         <v>45</v>
       </c>
       <c r="F70" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G70" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9480,7 +9034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B71" s="16" t="s">
         <v>100</v>
       </c>
@@ -9494,7 +9048,7 @@
         <v>43</v>
       </c>
       <c r="F71" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G71" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9505,7 +9059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B72" s="16" t="s">
         <v>101</v>
       </c>
@@ -9520,7 +9074,7 @@
         <v>102</v>
       </c>
       <c r="F72" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G72" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9531,7 +9085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B73" s="16" t="s">
         <v>103</v>
       </c>
@@ -9546,7 +9100,7 @@
         <v>102</v>
       </c>
       <c r="F73" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G73" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9557,7 +9111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B74" s="16" t="s">
         <v>104</v>
       </c>
@@ -9572,7 +9126,7 @@
         <v>102</v>
       </c>
       <c r="F74" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G74" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9583,12 +9137,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B75" s="16" t="s">
         <v>92</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D75" s="20">
         <v>0.25</v>
@@ -9597,7 +9151,7 @@
         <v>43</v>
       </c>
       <c r="F75" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G75" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9608,7 +9162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B76" s="16" t="s">
         <v>94</v>
       </c>
@@ -9622,7 +9176,7 @@
         <v>43</v>
       </c>
       <c r="F76" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G76" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9633,7 +9187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B77" s="16" t="s">
         <v>96</v>
       </c>
@@ -9647,7 +9201,7 @@
         <v>43</v>
       </c>
       <c r="F77" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G77" s="70" t="str">
         <f t="shared" si="0"/>
@@ -9658,7 +9212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B78" s="16" t="s">
         <v>97</v>
       </c>
@@ -9672,20 +9226,20 @@
         <v>43</v>
       </c>
       <c r="F78" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G78" s="70" t="str">
         <f t="shared" ref="G78:G81" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H78" s="138" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="I78" s="111">
         <v>4.5</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B79" s="16" t="s">
         <v>106</v>
       </c>
@@ -9700,7 +9254,7 @@
         <v>43</v>
       </c>
       <c r="F79" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G79" s="70" t="str">
         <f t="shared" si="2"/>
@@ -9711,7 +9265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B80" s="16" t="s">
         <v>107</v>
       </c>
@@ -9726,7 +9280,7 @@
         <v>43</v>
       </c>
       <c r="F80" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G80" s="70" t="str">
         <f t="shared" si="2"/>
@@ -9737,7 +9291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B81" s="81"/>
       <c r="C81" s="32"/>
       <c r="D81" s="82"/>
@@ -9750,9 +9304,9 @@
       <c r="H81" s="32"/>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B82" s="97" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C82" s="76"/>
       <c r="D82" s="77"/>
@@ -9762,7 +9316,7 @@
       <c r="H82" s="79"/>
       <c r="I82" s="80"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B83" s="16" t="s">
         <v>152</v>
       </c>
@@ -9777,7 +9331,7 @@
         <v>44</v>
       </c>
       <c r="F83" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G83" s="70" t="str">
         <f t="shared" ref="G83:G93" si="3">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F83,"/Readme.md"),"Ver")</f>
@@ -9788,7 +9342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B84" s="16" t="s">
         <v>153</v>
       </c>
@@ -9803,7 +9357,7 @@
         <v>155</v>
       </c>
       <c r="F84" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G84" s="70" t="str">
         <f t="shared" si="3"/>
@@ -9814,7 +9368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B85" s="16" t="s">
         <v>164</v>
       </c>
@@ -9829,7 +9383,7 @@
         <v>44</v>
       </c>
       <c r="F85" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G85" s="70" t="str">
         <f t="shared" si="3"/>
@@ -9840,7 +9394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B86" s="16" t="s">
         <v>157</v>
       </c>
@@ -9855,7 +9409,7 @@
         <v>102</v>
       </c>
       <c r="F86" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G86" s="70" t="str">
         <f t="shared" si="3"/>
@@ -9866,7 +9420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B87" s="16" t="s">
         <v>159</v>
       </c>
@@ -9881,7 +9435,7 @@
         <v>43</v>
       </c>
       <c r="F87" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G87" s="70" t="str">
         <f t="shared" si="3"/>
@@ -9892,7 +9446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B88" s="16" t="s">
         <v>161</v>
       </c>
@@ -9907,7 +9461,7 @@
         <v>43</v>
       </c>
       <c r="F88" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G88" s="70" t="str">
         <f t="shared" si="3"/>
@@ -9918,7 +9472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B89" s="16" t="s">
         <v>172</v>
       </c>
@@ -9932,20 +9486,20 @@
         <v>44</v>
       </c>
       <c r="F89" s="55" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G89" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="H89" s="160" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="I89" s="162">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B90" s="16" t="s">
         <v>173</v>
       </c>
@@ -9959,16 +9513,18 @@
         <v>102</v>
       </c>
       <c r="F90" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G90" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="H90" s="48"/>
-      <c r="I90" s="8"/>
-    </row>
-    <row r="91" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="I90" s="161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B91" s="16" t="s">
         <v>36</v>
       </c>
@@ -9982,16 +9538,18 @@
         <v>102</v>
       </c>
       <c r="F91" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G91" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="H91" s="48"/>
-      <c r="I91" s="8"/>
-    </row>
-    <row r="92" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="I91" s="161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" ht="33" x14ac:dyDescent="0.45">
       <c r="B92" s="16" t="s">
         <v>37</v>
       </c>
@@ -10005,16 +9563,18 @@
         <v>102</v>
       </c>
       <c r="F92" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G92" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Ver</v>
       </c>
       <c r="H92" s="48"/>
-      <c r="I92" s="8"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I92" s="161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B93" s="24"/>
       <c r="C93" s="96"/>
       <c r="D93" s="82"/>
@@ -10027,26 +9587,26 @@
       <c r="H93" s="32"/>
       <c r="I93" s="6"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B94" s="84" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.45">
       <c r="H95" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I95" s="31">
         <f>AVERAGE(I7:I93)</f>
-        <v>4.7661290322580649</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+        <v>4.8066666666666666</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B96" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B97" s="5" t="s">
         <v>134</v>
       </c>
@@ -10054,7 +9614,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B98" s="86" t="s">
         <v>136</v>
       </c>
@@ -10063,7 +9623,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B99" s="86" t="s">
         <v>139</v>
       </c>
@@ -10072,7 +9632,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B100" s="86" t="s">
         <v>138</v>
       </c>
@@ -10081,7 +9641,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B101" s="86" t="s">
         <v>35</v>
       </c>
@@ -10090,7 +9650,7 @@
         <v>7.0560000000000018</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B102" s="86" t="s">
         <v>34</v>
       </c>
@@ -10099,7 +9659,7 @@
         <v>52.943999999999996</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B103" s="88" t="s">
         <v>137</v>
       </c>
@@ -10108,7 +9668,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B104" s="90" t="s">
         <v>56</v>
       </c>
@@ -10117,7 +9677,7 @@
         <v>0.73584905660377353</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B105" s="81" t="s">
         <v>86</v>
       </c>
@@ -10142,46 +9702,46 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0208CCDC-4764-4F83-B616-E933FFE8EBF4}">
   <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B3" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B4" s="106" t="s">
         <v>136</v>
       </c>
       <c r="C4" s="106" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D4" s="106" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B5" s="105" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C5" s="105" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B6" s="105" t="str">
         <f>_xlfn.CONCAT(SumUDig,",",SumUDig)</f>
         <v>25,25</v>
@@ -10195,7 +9755,7 @@
         <v>25,29</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B7" s="105" t="str">
         <f>_xlfn.CONCAT("@",'2.ArquitectonicaEstructural'!D15,",",0)</f>
         <v>@33,0</v>
@@ -10209,7 +9769,7 @@
         <v>@33,0</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B8" s="105" t="str">
         <f>_xlfn.CONCAT("@0,",'2.ArquitectonicaEstructural'!D16)</f>
         <v>@0,53</v>
@@ -10223,7 +9783,7 @@
         <v>@0,39</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B9" s="105" t="str">
         <f>_xlfn.CONCAT("@",-'2.ArquitectonicaEstructural'!D15,",",0)</f>
         <v>@-33,0</v>
@@ -10237,7 +9797,7 @@
         <v>@-33,0</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B10" s="105" t="str">
         <f>_xlfn.CONCAT("@0,",-'2.ArquitectonicaEstructural'!D16)</f>
         <v>@0,-53</v>
@@ -10251,7 +9811,7 @@
         <v>@0,-39</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B11" s="105"/>
       <c r="C11" s="105"/>
       <c r="D11" s="105"/>
@@ -10263,54 +9823,55 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:I46"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:K46"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="49" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="49" customWidth="1"/>
+    <col min="10" max="10" width="2.796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.86328125" style="164"/>
+    <col min="12" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="166" t="s">
+    <row r="4" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B4" s="167" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-    </row>
-    <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+    </row>
+    <row r="5" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -10323,10 +9884,10 @@
       <c r="E6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="201"/>
+      <c r="G6" s="202"/>
       <c r="H6" s="22" t="s">
         <v>16</v>
       </c>
@@ -10334,9 +9895,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B7" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -10346,12 +9907,12 @@
       <c r="H7" s="47"/>
       <c r="I7" s="38"/>
     </row>
-    <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:11" ht="51" x14ac:dyDescent="0.6">
       <c r="B8" s="16" t="s">
         <v>193</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -10360,18 +9921,25 @@
         <v>102</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G8" s="53" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="39"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H8" s="138" t="s">
+        <v>561</v>
+      </c>
+      <c r="I8" s="111">
+        <v>0</v>
+      </c>
+      <c r="K8" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B9" s="16" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>194</v>
@@ -10383,18 +9951,23 @@
         <v>102</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G9" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="39"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I9" s="159">
+        <v>5</v>
+      </c>
+      <c r="K9" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B10" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>194</v>
@@ -10406,18 +9979,23 @@
         <v>102</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G10" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="I10" s="159">
+        <v>5</v>
+      </c>
+      <c r="K10" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B11" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>197</v>
@@ -10429,18 +10007,23 @@
         <v>102</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G11" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="I11" s="159">
+        <v>5</v>
+      </c>
+      <c r="K11" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B12" s="27" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>195</v>
@@ -10452,18 +10035,23 @@
         <v>102</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G12" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="28"/>
-      <c r="I12" s="40"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I12" s="159">
+        <v>5</v>
+      </c>
+      <c r="K12" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B13" s="27" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>196</v>
@@ -10475,16 +10063,21 @@
         <v>102</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G13" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="28"/>
-      <c r="I13" s="40"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I13" s="163">
+        <v>5</v>
+      </c>
+      <c r="K13" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B14" s="16" t="s">
         <v>179</v>
       </c>
@@ -10498,16 +10091,23 @@
         <v>102</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G14" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H14" s="138" t="s">
+        <v>562</v>
+      </c>
+      <c r="I14" s="163">
+        <v>5</v>
+      </c>
+      <c r="K14" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B15" s="16" t="s">
         <v>180</v>
       </c>
@@ -10521,16 +10121,21 @@
         <v>102</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G15" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H15" s="138"/>
+      <c r="I15" s="163">
+        <v>5</v>
+      </c>
+      <c r="K15" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B16" s="27" t="s">
         <v>181</v>
       </c>
@@ -10544,18 +10149,23 @@
         <v>102</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G16" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="40"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H16" s="138"/>
+      <c r="I16" s="163">
+        <v>5</v>
+      </c>
+      <c r="K16" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B17" s="27" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>183</v>
@@ -10567,16 +10177,21 @@
         <v>102</v>
       </c>
       <c r="F17" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G17" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H17" s="28"/>
-      <c r="I17" s="40"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I17" s="163">
+        <v>5</v>
+      </c>
+      <c r="K17" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B18" s="27" t="s">
         <v>182</v>
       </c>
@@ -10590,7 +10205,7 @@
         <v>102</v>
       </c>
       <c r="F18" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G18" s="53" t="str">
         <f t="shared" si="0"/>
@@ -10598,13 +10213,16 @@
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="40"/>
-    </row>
-    <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
+      <c r="K18" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B19" s="27" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -10613,18 +10231,21 @@
         <v>102</v>
       </c>
       <c r="F19" s="55" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G19" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H19" s="28"/>
-      <c r="I19" s="40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I19" s="163">
+        <v>5</v>
+      </c>
+      <c r="K19" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B20" s="27" t="s">
         <v>192</v>
       </c>
@@ -10638,7 +10259,7 @@
         <v>102</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G20" s="53" t="str">
         <f t="shared" si="0"/>
@@ -10646,8 +10267,11 @@
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="40"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="K20" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B21" s="27"/>
       <c r="C21" s="28"/>
       <c r="D21" s="29"/>
@@ -10659,10 +10283,13 @@
       </c>
       <c r="H21" s="28"/>
       <c r="I21" s="40"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="K21" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B22" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -10672,7 +10299,7 @@
       <c r="H22" s="47"/>
       <c r="I22" s="38"/>
     </row>
-    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:11" ht="38.25" x14ac:dyDescent="0.6">
       <c r="B23" s="16" t="s">
         <v>184</v>
       </c>
@@ -10687,16 +10314,21 @@
         <v>44</v>
       </c>
       <c r="F23" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G23" s="53" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H23" s="19"/>
-      <c r="I23" s="39"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I23" s="39">
+        <v>5</v>
+      </c>
+      <c r="K23" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B24" s="16" t="s">
         <v>186</v>
       </c>
@@ -10710,16 +10342,21 @@
         <v>53</v>
       </c>
       <c r="F24" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G24" s="53" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H24" s="19"/>
-      <c r="I24" s="39"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I24" s="39">
+        <v>5</v>
+      </c>
+      <c r="K24" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B25" s="16" t="s">
         <v>185</v>
       </c>
@@ -10733,16 +10370,21 @@
         <v>53</v>
       </c>
       <c r="F25" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G25" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
       <c r="H25" s="19"/>
-      <c r="I25" s="39"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="I25" s="39">
+        <v>5</v>
+      </c>
+      <c r="K25" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="51" x14ac:dyDescent="0.6">
       <c r="B26" s="16" t="s">
         <v>188</v>
       </c>
@@ -10757,16 +10399,21 @@
         <v>102</v>
       </c>
       <c r="F26" s="55" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G26" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
       <c r="H26" s="19"/>
-      <c r="I26" s="39"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I26" s="39">
+        <v>5</v>
+      </c>
+      <c r="K26" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
@@ -10779,143 +10426,143 @@
       <c r="H27" s="25"/>
       <c r="I27" s="41"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.6">
       <c r="H28" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I28" s="49">
         <f>AVERAGE(I7:I27)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B29" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B30" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C30" s="101" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B31" s="86" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B32" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="C32" s="102" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B33" s="86" t="s">
+        <v>350</v>
+      </c>
+      <c r="C33" s="102" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B34" s="86" t="s">
+        <v>351</v>
+      </c>
+      <c r="C34" s="102" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B35" s="81" t="s">
+        <v>355</v>
+      </c>
+      <c r="C35" s="103" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B37" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B38" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C38" s="101" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B39" s="86" t="s">
+        <v>329</v>
+      </c>
+      <c r="C39" s="102" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B40" s="86" t="s">
+        <v>333</v>
+      </c>
+      <c r="C40" s="102" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B41" s="86" t="s">
+        <v>357</v>
+      </c>
+      <c r="C41" s="102" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B42" s="86" t="s">
+        <v>334</v>
+      </c>
+      <c r="C42" s="102" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B43" s="86" t="s">
+        <v>336</v>
+      </c>
+      <c r="C43" s="102" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B44" s="86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" s="102" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B45" s="86" t="s">
+        <v>338</v>
+      </c>
+      <c r="C45" s="102" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B46" s="81" t="s">
+        <v>330</v>
+      </c>
+      <c r="C46" s="103" t="s">
         <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B30" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C30" s="101" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B31" s="86" t="s">
-        <v>352</v>
-      </c>
-      <c r="C31" s="102" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B32" s="86" t="s">
-        <v>353</v>
-      </c>
-      <c r="C32" s="102" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B33" s="86" t="s">
-        <v>354</v>
-      </c>
-      <c r="C33" s="102" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B34" s="86" t="s">
-        <v>355</v>
-      </c>
-      <c r="C34" s="102" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B35" s="81" t="s">
-        <v>359</v>
-      </c>
-      <c r="C35" s="103" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B37" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B38" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C38" s="101" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B39" s="86" t="s">
-        <v>333</v>
-      </c>
-      <c r="C39" s="102" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B40" s="86" t="s">
-        <v>337</v>
-      </c>
-      <c r="C40" s="102" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B41" s="86" t="s">
-        <v>361</v>
-      </c>
-      <c r="C41" s="102" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B42" s="86" t="s">
-        <v>338</v>
-      </c>
-      <c r="C42" s="102" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B43" s="86" t="s">
-        <v>340</v>
-      </c>
-      <c r="C43" s="102" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B44" s="86" t="s">
-        <v>341</v>
-      </c>
-      <c r="C44" s="102" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B45" s="86" t="s">
-        <v>342</v>
-      </c>
-      <c r="C45" s="102" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B46" s="81" t="s">
-        <v>334</v>
-      </c>
-      <c r="C46" s="103" t="s">
-        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -10933,54 +10580,55 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FBD0B4-938E-4D04-BE03-979DB3A57126}">
-  <dimension ref="B2:I23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:K23"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="49" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="49" customWidth="1"/>
+    <col min="10" max="10" width="2.796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="164"/>
+    <col min="12" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="166" t="s">
+    <row r="4" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B4" s="167" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -10993,10 +10641,10 @@
       <c r="E6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="200" t="s">
+      <c r="F6" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="201"/>
+      <c r="G6" s="202"/>
       <c r="H6" s="22" t="s">
         <v>16</v>
       </c>
@@ -11004,9 +10652,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B7" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -11016,7 +10664,7 @@
       <c r="H7" s="47"/>
       <c r="I7" s="38"/>
     </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B8" s="16" t="s">
         <v>202</v>
       </c>
@@ -11030,18 +10678,23 @@
         <v>43</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G8" s="53" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="138" t="s">
+        <v>567</v>
+      </c>
       <c r="I8" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+      <c r="K8" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B9" s="16" t="s">
         <v>206</v>
       </c>
@@ -11055,21 +10708,28 @@
         <v>43</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G9" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H9" s="19"/>
-      <c r="I9" s="39"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="H9" s="138" t="s">
+        <v>567</v>
+      </c>
+      <c r="I9" s="39">
+        <v>5</v>
+      </c>
+      <c r="K9" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B10" s="16" t="s">
         <v>204</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
@@ -11078,16 +10738,23 @@
         <v>205</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G10" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H10" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I10" s="39">
+        <v>5</v>
+      </c>
+      <c r="K10" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B11" s="16" t="s">
         <v>207</v>
       </c>
@@ -11101,21 +10768,28 @@
         <v>43</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G11" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="H11" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I11" s="39">
+        <v>5</v>
+      </c>
+      <c r="K11" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B12" s="16" t="s">
         <v>212</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -11125,16 +10799,23 @@
         <v>43</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G12" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="H12" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I12" s="39">
+        <v>5</v>
+      </c>
+      <c r="K12" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B13" s="16" t="s">
         <v>203</v>
       </c>
@@ -11148,45 +10829,59 @@
         <v>43</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G13" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H13" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I13" s="39">
+        <v>5</v>
+      </c>
+      <c r="K13" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B14" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G14" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="H14" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I14" s="39">
+        <v>5</v>
+      </c>
+      <c r="K14" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="33" x14ac:dyDescent="0.6">
       <c r="B15" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>220</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>221</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -11195,21 +10890,28 @@
         <v>43</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G15" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="H15" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I15" s="39">
+        <v>5</v>
+      </c>
+      <c r="K15" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="33" x14ac:dyDescent="0.6">
       <c r="B16" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -11219,16 +10921,23 @@
         <v>43</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G16" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="39"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H16" s="138" t="s">
+        <v>568</v>
+      </c>
+      <c r="I16" s="39">
+        <v>5</v>
+      </c>
+      <c r="K16" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B17" s="16"/>
       <c r="C17" s="19"/>
       <c r="D17" s="15"/>
@@ -11241,9 +10950,9 @@
       <c r="H17" s="19"/>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B18" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -11253,76 +10962,91 @@
       <c r="H18" s="47"/>
       <c r="I18" s="38"/>
     </row>
-    <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:11" ht="38.25" x14ac:dyDescent="0.6">
       <c r="B19" s="16" t="s">
-        <v>224</v>
+        <v>564</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>214</v>
+      <c r="D19" s="20">
+        <v>186</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>102</v>
       </c>
       <c r="F19" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G19" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H19" s="19"/>
-      <c r="I19" s="39"/>
-    </row>
-    <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="I19" s="39">
+        <v>5</v>
+      </c>
+      <c r="K19" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="38.25" x14ac:dyDescent="0.6">
       <c r="B20" s="16" t="s">
-        <v>225</v>
+        <v>565</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>214</v>
+      <c r="D20" s="20">
+        <v>36</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>102</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G20" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H20" s="19"/>
-      <c r="I20" s="39"/>
-    </row>
-    <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="I20" s="39">
+        <v>5</v>
+      </c>
+      <c r="K20" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="38.25" x14ac:dyDescent="0.6">
       <c r="B21" s="16" t="s">
-        <v>226</v>
+        <v>566</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>214</v>
+      <c r="D21" s="20">
+        <v>90</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>102</v>
       </c>
       <c r="F21" s="55" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G21" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H21" s="19"/>
-      <c r="I21" s="39"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I21" s="39">
+        <v>5</v>
+      </c>
+      <c r="K21" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
@@ -11332,13 +11056,13 @@
       <c r="H22" s="25"/>
       <c r="I22" s="41"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.6">
       <c r="H23" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I23" s="49">
         <f>AVERAGE(I7:I22)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11353,54 +11077,55 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
-  <dimension ref="B2:I17"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:K17"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="49" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="49" customWidth="1"/>
+    <col min="10" max="10" width="2.796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="164"/>
+    <col min="12" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="166" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="167"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="167"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B4" s="167" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.6">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="168"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -11413,10 +11138,10 @@
       <c r="E6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="195" t="s">
+      <c r="F6" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="196"/>
+      <c r="G6" s="197"/>
       <c r="H6" s="22" t="s">
         <v>16</v>
       </c>
@@ -11424,12 +11149,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B7" s="16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
@@ -11438,7 +11163,7 @@
         <v>102</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G7" s="53" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -11446,15 +11171,18 @@
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+      <c r="K7" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B8" s="16" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
@@ -11463,21 +11191,26 @@
         <v>102</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G8" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H8" s="19"/>
-      <c r="I8" s="39"/>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="I8" s="39">
+        <v>5</v>
+      </c>
+      <c r="K8" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B9" s="16" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
@@ -11486,21 +11219,26 @@
         <v>102</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G9" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="39"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="I9" s="39">
+        <v>5</v>
+      </c>
+      <c r="K9" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B10" s="16" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
@@ -11509,18 +11247,23 @@
         <v>102</v>
       </c>
       <c r="F10" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G10" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="39"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I10" s="39">
+        <v>5</v>
+      </c>
+      <c r="K10" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B11" s="16" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>194</v>
@@ -11532,18 +11275,23 @@
         <v>102</v>
       </c>
       <c r="F11" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G11" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="39"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I11" s="39">
+        <v>5</v>
+      </c>
+      <c r="K11" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B12" s="16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>194</v>
@@ -11555,18 +11303,20 @@
         <v>102</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G12" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="19"/>
-      <c r="I12" s="39"/>
-    </row>
-    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="I12" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="33" x14ac:dyDescent="0.6">
       <c r="B13" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>197</v>
@@ -11578,18 +11328,20 @@
         <v>102</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G13" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="39"/>
-    </row>
-    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="I13" s="39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="25.5" x14ac:dyDescent="0.6">
       <c r="B14" s="16" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>195</v>
@@ -11601,18 +11353,23 @@
         <v>102</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G14" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="19"/>
-      <c r="I14" s="39"/>
-    </row>
-    <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="I14" s="39">
+        <v>5</v>
+      </c>
+      <c r="K14" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B15" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>196</v>
@@ -11624,16 +11381,21 @@
         <v>102</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G15" s="53" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H15" s="19"/>
-      <c r="I15" s="39"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I15" s="39">
+        <v>5</v>
+      </c>
+      <c r="K15" s="164" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.6">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
       <c r="D16" s="36"/>
@@ -11646,13 +11408,13 @@
       <c r="H16" s="25"/>
       <c r="I16" s="41"/>
     </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:9" x14ac:dyDescent="0.6">
       <c r="H17" s="42" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I17" s="49">
         <f>AVERAGE(I7:I16)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
